--- a/experiment/ELAN_bestx4/Test/results-Manga109/Manga109.xlsx
+++ b/experiment/ELAN_bestx4/Test/results-Manga109/Manga109.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.58</v>
+        <v>28.68</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8207</v>
+        <v>0.8229</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.97</v>
+        <v>30.99</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8119</v>
+        <v>0.8122</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.4</v>
+        <v>28.49</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8428</v>
+        <v>0.8448</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36.04</v>
+        <v>36.09</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9474</v>
+        <v>0.9478</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39.25</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9756</v>
+        <v>0.9747</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.22</v>
+        <v>30.34</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9151</v>
+        <v>0.9164</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.16</v>
+        <v>33.35</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9543</v>
+        <v>0.9556</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.31</v>
+        <v>27.44</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.8943</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30.84</v>
+        <v>30.85</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9255</v>
+        <v>0.9263</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.81</v>
+        <v>29.89</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8962</v>
+        <v>0.8977000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29.9</v>
+        <v>30.11</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9489</v>
+        <v>0.9506</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.25</v>
+        <v>28.33</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8636</v>
+        <v>0.8656</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33.58</v>
+        <v>33.53</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9614</v>
+        <v>0.9619</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9011</v>
+        <v>0.9019</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.76</v>
+        <v>29.04</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9159</v>
+        <v>0.9185</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.75</v>
+        <v>27.83</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9061</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.13</v>
+        <v>31.25</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9556</v>
+        <v>0.9569</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34.37</v>
+        <v>34.53</v>
       </c>
       <c r="C19" t="n">
-        <v>0.976</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31.01</v>
+        <v>31.03</v>
       </c>
       <c r="C20" t="n">
-        <v>0.903</v>
+        <v>0.9034</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.98</v>
+        <v>33.09</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9747</v>
+        <v>0.9756</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9206</v>
+        <v>0.9215</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>31.88</v>
+        <v>32.08</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9316</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.36</v>
+        <v>30.46</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9127</v>
+        <v>0.9142</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>37.23</v>
+        <v>37.36</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9702</v>
+        <v>0.9708</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28.97</v>
+        <v>29.11</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9529</v>
+        <v>0.9538</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>31.31</v>
+        <v>31.34</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9391</v>
+        <v>0.9398</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37.95</v>
+        <v>38.24</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9761</v>
+        <v>0.9769</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.71</v>
+        <v>31.69</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9324</v>
+        <v>0.9325</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9582000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31.52</v>
+        <v>31.66</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9426</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26.99</v>
+        <v>26.96</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9363</v>
+        <v>0.9373</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27.94</v>
+        <v>28.04</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9301</v>
+        <v>0.9316</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.52</v>
+        <v>32.61</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8937</v>
+        <v>0.8956</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28.8</v>
+        <v>28.84</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7458</v>
+        <v>0.7466</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26.6</v>
+        <v>26.61</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8716</v>
+        <v>0.8723</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.75</v>
+        <v>31.84</v>
       </c>
       <c r="C37" t="n">
-        <v>0.912</v>
+        <v>0.9133</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27.73</v>
+        <v>27.82</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8635</v>
+        <v>0.8652</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>34.85</v>
+        <v>34.95</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9688</v>
+        <v>0.9694</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>35.05</v>
+        <v>35.13</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9611</v>
+        <v>0.9616</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>28.03</v>
+        <v>28.28</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8907</v>
+        <v>0.8967000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.07</v>
+        <v>31.03</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8665</v>
+        <v>0.8672</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32.99</v>
+        <v>33.04</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9146</v>
+        <v>0.9152</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>21.02</v>
+        <v>21.1</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7431</v>
+        <v>0.7473</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>35.19</v>
+        <v>35.43</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9757</v>
+        <v>0.9767</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25.15</v>
+        <v>25.21</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9152</v>
+        <v>0.9164</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>27.82</v>
+        <v>27.92</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9009</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>34.49</v>
+        <v>34.63</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9502</v>
+        <v>0.9517</v>
       </c>
     </row>
     <row r="49">
@@ -1066,7 +1066,7 @@
         <v>27.08</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8678</v>
+        <v>0.8682</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28.93</v>
+        <v>29.02</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9186</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26.72</v>
+        <v>26.79</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7619</v>
+        <v>0.7639</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30.33</v>
+        <v>30.41</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9449</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>33.3</v>
+        <v>33.38</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9445</v>
+        <v>0.9454</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>36.39</v>
+        <v>36.41</v>
       </c>
       <c r="C54" t="n">
-        <v>0.904</v>
+        <v>0.9044</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>35.51</v>
+        <v>35.62</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9607</v>
+        <v>0.962</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>22.74</v>
+        <v>22.79</v>
       </c>
       <c r="C56" t="n">
-        <v>0.726</v>
+        <v>0.7297</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>33.05</v>
+        <v>33.01</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9644</v>
+        <v>0.9641</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.58</v>
+        <v>31.95</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9456</v>
+        <v>0.9473</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>32.11</v>
+        <v>32.18</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9438</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>23.77</v>
+        <v>23.82</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7601</v>
+        <v>0.7637</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>33.35</v>
+        <v>33.53</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9675</v>
+        <v>0.9683</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.81</v>
+        <v>31.92</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9445</v>
+        <v>0.9453</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>30.94</v>
+        <v>31.03</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9475</v>
+        <v>0.9491000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>35.03</v>
+        <v>35.11</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9661</v>
+        <v>0.9668</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>33.98</v>
+        <v>34</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9261</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.23</v>
+        <v>25.38</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9282</v>
+        <v>0.9308</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>32.22</v>
+        <v>32.32</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9397</v>
+        <v>0.9407</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>33.15</v>
+        <v>33.2</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9305</v>
+        <v>0.9314</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>31.81</v>
+        <v>31.88</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9404</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>28.29</v>
+        <v>28.41</v>
       </c>
       <c r="C70" t="n">
-        <v>0.9202</v>
+        <v>0.9224</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>30.99</v>
+        <v>31.05</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9365</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>27.94</v>
+        <v>27.96</v>
       </c>
       <c r="C72" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.7133</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>34.82</v>
+        <v>34.8</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9579</v>
+        <v>0.9582000000000001</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>33.96</v>
+        <v>34.05</v>
       </c>
       <c r="C74" t="n">
-        <v>0.9498</v>
+        <v>0.9509</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>28.1</v>
+        <v>28.26</v>
       </c>
       <c r="C75" t="n">
-        <v>0.8882</v>
+        <v>0.8905</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>29.68</v>
+        <v>29.79</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9</v>
+        <v>0.9019</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.59</v>
+        <v>30.68</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9308</v>
+        <v>0.9316</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>30.16</v>
+        <v>30.27</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8769</v>
+        <v>0.8784999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>28.17</v>
+        <v>28.29</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8095</v>
+        <v>0.8108</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>31.03</v>
+        <v>31.11</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9334</v>
+        <v>0.9347</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>31.09</v>
+        <v>31.21</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9428</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>30.03</v>
+        <v>30.11</v>
       </c>
       <c r="C82" t="n">
-        <v>0.8747</v>
+        <v>0.8761</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>32.01</v>
+        <v>32.1</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9031</v>
+        <v>0.9045</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>31.58</v>
+        <v>31.74</v>
       </c>
       <c r="C84" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9581</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>27.64</v>
+        <v>27.8</v>
       </c>
       <c r="C85" t="n">
-        <v>0.9409</v>
+        <v>0.9425</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>32.5</v>
+        <v>32.62</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9313</v>
+        <v>0.9329</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>28.46</v>
+        <v>28.55</v>
       </c>
       <c r="C87" t="n">
-        <v>0.873</v>
+        <v>0.8746</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>35.42</v>
+        <v>35.3</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9500999999999999</v>
+        <v>0.9503</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>33.77</v>
+        <v>33.83</v>
       </c>
       <c r="C89" t="n">
-        <v>0.9605</v>
+        <v>0.9613</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>30.33</v>
+        <v>30.38</v>
       </c>
       <c r="C90" t="n">
-        <v>0.9218</v>
+        <v>0.9224</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.37</v>
+        <v>25.51</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8595</v>
+        <v>0.862</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>28.76</v>
+        <v>28.92</v>
       </c>
       <c r="C92" t="n">
-        <v>0.9114</v>
+        <v>0.9142</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>27.18</v>
+        <v>27.24</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9423</v>
+        <v>0.9435</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>21.07</v>
+        <v>21.13</v>
       </c>
       <c r="C94" t="n">
-        <v>0.7353</v>
+        <v>0.7387</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>34</v>
+        <v>34.09</v>
       </c>
       <c r="C95" t="n">
-        <v>0.9539</v>
+        <v>0.9547</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.76</v>
+        <v>26.89</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8806</v>
+        <v>0.8827</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>30.05</v>
+        <v>30.13</v>
       </c>
       <c r="C97" t="n">
-        <v>0.9046</v>
+        <v>0.9063</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>32.54</v>
+        <v>32.61</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8756</v>
+        <v>0.8764</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>29.24</v>
+        <v>29.38</v>
       </c>
       <c r="C99" t="n">
-        <v>0.9633</v>
+        <v>0.9644</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25.89</v>
+        <v>25.87</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.7561</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>23.7</v>
+        <v>23.83</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8869</v>
+        <v>0.8899</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.34</v>
+        <v>27.41</v>
       </c>
       <c r="C102" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="103">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>22.67</v>
+        <v>22.83</v>
       </c>
       <c r="C103" t="n">
-        <v>0.8012</v>
+        <v>0.8017</v>
       </c>
     </row>
     <row r="104">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>36.52</v>
+        <v>36.99</v>
       </c>
       <c r="C104" t="n">
-        <v>0.9716</v>
+        <v>0.9722</v>
       </c>
     </row>
     <row r="105">
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>28.89</v>
+        <v>28.96</v>
       </c>
       <c r="C105" t="n">
-        <v>0.9069</v>
+        <v>0.9084</v>
       </c>
     </row>
     <row r="106">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>33.38</v>
+        <v>33.54</v>
       </c>
       <c r="C106" t="n">
-        <v>0.971</v>
+        <v>0.9724</v>
       </c>
     </row>
     <row r="107">
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>29.63</v>
+        <v>29.69</v>
       </c>
       <c r="C107" t="n">
-        <v>0.885</v>
+        <v>0.8862</v>
       </c>
     </row>
     <row r="108">
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>36.83</v>
+        <v>36.64</v>
       </c>
       <c r="C108" t="n">
-        <v>0.9379</v>
+        <v>0.9378</v>
       </c>
     </row>
     <row r="109">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>31.64</v>
+        <v>31.7</v>
       </c>
       <c r="C109" t="n">
-        <v>0.8629</v>
+        <v>0.8635</v>
       </c>
     </row>
     <row r="110">
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>28.42</v>
+        <v>28.55</v>
       </c>
       <c r="C110" t="n">
-        <v>0.9105</v>
+        <v>0.9136</v>
       </c>
     </row>
     <row r="111">
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>30.59</v>
+        <v>30.68</v>
       </c>
       <c r="C111" t="n">
-        <v>0.908</v>
+        <v>0.9094</v>
       </c>
     </row>
   </sheetData>
